--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_223_R23.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_223_R23.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2557</v>
+        <v>4.9897</v>
       </c>
       <c r="E2" t="n">
-        <v>0.893</v>
+        <v>4.5461</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3626</v>
+        <v>0.4436</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.2178</v>
+        <v>3.6609</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3145</v>
+        <v>-2.1945</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.5324</v>
+        <v>5.8554</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.8894</v>
+        <v>4.3935</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6785</v>
+        <v>-2.2547</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2109</v>
+        <v>6.6483</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3284</v>
+        <v>-0.7326</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9931</v>
+        <v>0.0602</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3215</v>
+        <v>-0.7929</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0154</v>
+        <v>0.232</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0154</v>
+        <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.042</v>
+        <v>0.0246</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.7177</v>
+        <v>0.2401</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6757</v>
+        <v>-0.2155</v>
       </c>
       <c r="V2" t="n">
-        <v>3.5002</v>
+        <v>1.0722</v>
       </c>
       <c r="W2" t="n">
-        <v>3.5002</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7575</v>
+        <v>4.584</v>
       </c>
       <c r="E3" t="n">
-        <v>2.115</v>
+        <v>1.5575</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6425</v>
+        <v>3.0266</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3676</v>
+        <v>-1.2178</v>
       </c>
       <c r="H3" t="n">
-        <v>0.742</v>
+        <v>0.3145</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6257</v>
+        <v>-1.5324</v>
       </c>
       <c r="J3" t="n">
-        <v>2.036</v>
+        <v>-0.8894</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3564</v>
+        <v>-0.6785</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6796</v>
+        <v>-0.2109</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6683</v>
+        <v>-0.3284</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3856</v>
+        <v>0.9931</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0539</v>
+        <v>-1.3215</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1598</v>
+        <v>3.0154</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3719</v>
+        <v>-0.7136</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2388</v>
+        <v>-1.0532</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1331</v>
+        <v>0.3396</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1418</v>
+        <v>3.5002</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.5002</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3418</v>
+        <v>3.4344</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3351</v>
+        <v>1.5567</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0067</v>
+        <v>1.8777</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6609</v>
+        <v>1.3676</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1945</v>
+        <v>0.742</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8554</v>
+        <v>0.6257</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3935</v>
+        <v>2.036</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.2547</v>
+        <v>0.3564</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6483</v>
+        <v>1.6796</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7326</v>
+        <v>-0.6683</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0602</v>
+        <v>0.3856</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7929</v>
+        <v>-1.0539</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6232</v>
+        <v>1.0488</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9709</v>
+        <v>0.6805</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6524</v>
+        <v>0.3684</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>T. ODIASE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6196</v>
+        <v>0.4453</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7484</v>
+        <v>0.9611</v>
       </c>
       <c r="F5" t="n">
-        <v>3.368</v>
+        <v>-0.5158</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2888</v>
+        <v>-0.629</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0311</v>
+        <v>0.0301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2578</v>
+        <v>-0.6591</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2582</v>
+        <v>0.7722</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9943</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7361</v>
+        <v>0.184</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5471</v>
+        <v>-1.4012</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0254</v>
+        <v>-0.5581</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4783</v>
+        <v>-0.8431</v>
       </c>
       <c r="P5" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2817</v>
+        <v>0.1465</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9401</v>
+        <v>0.1889</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3416</v>
+        <v>-0.0424</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1829</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1107</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. ODIASE</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.337</v>
+        <v>0.1327</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8864</v>
+        <v>-1.0889</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5494</v>
+        <v>1.2216</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.629</v>
+        <v>-1.1942</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0301</v>
+        <v>1.4994</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6591</v>
+        <v>-2.6937</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7722</v>
+        <v>0.035</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5881999999999999</v>
+        <v>1.1462</v>
       </c>
       <c r="L6" t="n">
-        <v>0.184</v>
+        <v>-1.1112</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4012</v>
+        <v>-1.2293</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5581</v>
+        <v>0.3532</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8431</v>
+        <v>-1.5825</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0382</v>
+        <v>-0.0648</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1142</v>
+        <v>0.0358</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.076</v>
+        <v>-0.1006</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0257</v>
+        <v>-0.0902</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0456</v>
+        <v>-2.8532</v>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>2.7631</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1942</v>
+        <v>0.2888</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4994</v>
+        <v>0.0311</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.6937</v>
+        <v>0.2578</v>
       </c>
       <c r="J7" t="n">
-        <v>0.035</v>
+        <v>-0.2582</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1462</v>
+        <v>-0.9943</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1112</v>
+        <v>0.7361</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2293</v>
+        <v>0.5471</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3532</v>
+        <v>1.0254</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5825</v>
+        <v>-0.4783</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
         <v>2.5515</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2232</v>
+        <v>0.572</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0791</v>
+        <v>-0.1647</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3022</v>
+        <v>0.7367</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.1829</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.1107</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>Y. MADAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1332</v>
+        <v>-0.4731</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4535</v>
+        <v>-1.9204</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3203</v>
+        <v>1.4473</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3132</v>
+        <v>-1.2869</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1753</v>
+        <v>0.1452</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4885</v>
+        <v>-1.4321</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-1.5156</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0504</v>
+        <v>0.0203</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-1.5359</v>
       </c>
       <c r="M8" t="n">
-        <v>0.386</v>
+        <v>0.2287</v>
       </c>
       <c r="N8" t="n">
         <v>0.1249</v>
       </c>
       <c r="O8" t="n">
-        <v>0.261</v>
+        <v>0.1038</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5021</v>
+        <v>0.118</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2636</v>
+        <v>-0.4048</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2385</v>
+        <v>0.5228</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y. MADAR</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4566</v>
+        <v>-0.5714</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0384</v>
+        <v>-1.9253</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5817</v>
+        <v>1.354</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2869</v>
+        <v>-0.3132</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1452</v>
+        <v>0.1753</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4321</v>
+        <v>-0.4885</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5156</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0203</v>
+        <v>0.0504</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5359</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2287</v>
+        <v>0.386</v>
       </c>
       <c r="N9" t="n">
         <v>0.1249</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1038</v>
+        <v>0.261</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1344</v>
+        <v>0.0639</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5228</v>
+        <v>-0.2082</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6572</v>
+        <v>0.2721</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9187</v>
+        <v>-2.3214</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1549</v>
+        <v>-1.4904</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7638</v>
+        <v>-0.831</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9252</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0631</v>
+        <v>-0.4659</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8215</v>
+        <v>-0.1571</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2416</v>
+        <v>-0.3088</v>
       </c>
       <c r="V10" t="n">
         <v>0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9075</v>
+        <v>-3.5132</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5013</v>
+        <v>-5.3087</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5938</v>
+        <v>1.7955</v>
       </c>
       <c r="G11" t="n">
         <v>0.5684</v>
@@ -1312,13 +1312,13 @@
         <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0842</v>
+        <v>-0.6899</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1949</v>
+        <v>-1.0023</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1107</v>
+        <v>0.3123</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.869899999999999</v>
+        <v>6.616799999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.7126</v>
+        <v>-5.9655</v>
       </c>
       <c r="F12" t="n">
-        <v>12.5824</v>
+        <v>12.5826</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6806</v>
@@ -1369,7 +1369,7 @@
         <v>-3.2308</v>
       </c>
       <c r="L12" t="n">
-        <v>5.821</v>
+        <v>5.821000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-4.2704</v>
@@ -1390,13 +1390,13 @@
         <v>17.3965</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7074000000000003</v>
+        <v>0.03960000000000008</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.592</v>
+        <v>-1.845</v>
       </c>
       <c r="U12" t="n">
-        <v>1.884599999999999</v>
+        <v>1.8846</v>
       </c>
       <c r="V12" t="n">
         <v>2.4591</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5554</v>
+        <v>3.6398</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0247</v>
+        <v>3.1427</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.4971</v>
       </c>
       <c r="G13" t="n">
         <v>3.846</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1129</v>
+        <v>-0.0286</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0553</v>
+        <v>0.1733</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1682</v>
+        <v>-0.2018</v>
       </c>
       <c r="V13" t="n">
         <v>1.214</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4424</v>
+        <v>2.8476</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0574</v>
+        <v>0.6503</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4998</v>
+        <v>2.1973</v>
       </c>
       <c r="G14" t="n">
         <v>0.9162</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1902</v>
+        <v>0.215</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8057</v>
+        <v>-0.098</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6155</v>
+        <v>0.313</v>
       </c>
       <c r="V14" t="n">
         <v>0.7886</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7097</v>
+        <v>0.9526</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8032</v>
+        <v>-1.157</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5129</v>
+        <v>2.1096</v>
       </c>
       <c r="G15" t="n">
         <v>2.4537</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3979</v>
+        <v>0.6407</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0193</v>
+        <v>-0.3732</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4172</v>
+        <v>1.0139</v>
       </c>
       <c r="V15" t="n">
         <v>-1.214</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.07679999999999999</v>
+        <v>-0.395</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3968</v>
+        <v>-1.8686</v>
       </c>
       <c r="F17" t="n">
         <v>1.4736</v>
@@ -1780,10 +1780,10 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5623</v>
+        <v>0.0905</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1889</v>
+        <v>-0.2829</v>
       </c>
       <c r="U17" t="n">
         <v>0.3734</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4332</v>
+        <v>-0.6019</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2564</v>
+        <v>-0.4923</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1768</v>
+        <v>-0.1095</v>
       </c>
       <c r="G18" t="n">
         <v>-1.115</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6818</v>
+        <v>0.5131</v>
       </c>
       <c r="T18" t="n">
-        <v>0.637</v>
+        <v>0.4011</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3997</v>
+        <v>-1.888</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3807</v>
+        <v>-0.7346</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.019</v>
+        <v>-1.1534</v>
       </c>
       <c r="G19" t="n">
         <v>-0.07779999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0518</v>
+        <v>-0.4364</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2636</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2117</v>
+        <v>-0.3462</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6778999999999999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.173</v>
+        <v>-1.9041</v>
       </c>
       <c r="E20" t="n">
         <v>-2.8051</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6321</v>
+        <v>0.9009</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9943</v>
@@ -2014,13 +2014,13 @@
         <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0369</v>
+        <v>0.232</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4674</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4305</v>
+        <v>0.6994</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6778999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0253</v>
+        <v>-3.7057</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.5194</v>
+        <v>-6.4014</v>
       </c>
       <c r="F21" t="n">
-        <v>2.494</v>
+        <v>2.6957</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8633</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2091</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1766</v>
+        <v>-0.0587</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3857</v>
+        <v>0.5874</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2836</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.903</v>
+        <v>-5.0952</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6682</v>
+        <v>-3.1964</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2348</v>
+        <v>-1.8988</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1917</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7809</v>
+        <v>-0.973</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4857</v>
+        <v>-1.0139</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2952</v>
+        <v>0.0409</v>
       </c>
       <c r="V22" t="n">
         <v>-2.0026</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.869999999999999</v>
+        <v>-5.87</v>
       </c>
       <c r="E23" t="n">
-        <v>-12.5826</v>
+        <v>-12.5825</v>
       </c>
       <c r="F23" t="n">
         <v>6.7125</v>
@@ -2248,10 +2248,10 @@
         <v>11.5977</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7072999999999996</v>
+        <v>0.7073000000000002</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.8846</v>
+        <v>-1.8847</v>
       </c>
       <c r="U23" t="n">
         <v>2.592</v>
